--- a/stories/arbres/ATOM-DIF.COR.002-05.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Prune et Armand sont au parc avec papa. Ils se passent un ballon. Armand a un corps plus rond. Prune a un corps plus mince. Papa dit : le corps n'est pas une blague. On joue ensemble. Prune ne commente pas le corps. Elle passe le ballon. Armand le rend. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le corps n'est pas une blague.</t>
+          <t>Prune et Armand sont au parc avec papa. Ils se passent un ballon. Armand a un corps plus rond. Prune a un corps plus mince. Le corps n'est pas une blague. On joue ensemble. Prune ne commente pas le corps. Elle passe le ballon. Armand le rend. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Prune et Armand sont au parc avec papa. Ils se passent un ballon. Armand a un corps plus rond. Prune a un corps plus mince.
+papa|Le corps n'est pas une blague. On joue ensemble.
+narrateur|Prune ne commente pas le corps. Elle passe le ballon. Armand le rend. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le corps n'est pas une blague.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Prune joue avec Armand. Que fait-on ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Prune a joué avec Armand. Le corps n'était pas une blague.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Prune essuie ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.002-05.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Prune ne commente pas le corps. Elle passe le ballon. Armand le rend. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le corps n'est pas une blague.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Prune joue avec Armand. Que fait-on ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Prune a joué avec Armand. Le corps n'était pas une blague.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Papa range le ballon. Prune essuie ses mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.COR.002-05.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prune joue, le corps n'est pas une blague</t>
+          <t>Le bateau dans le sable</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un bateau de bois attend dans le sable, près de la fontaine. Raphaël et Aniss se passent un ballon. Le corps n'est pas une blague. Ils jouent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Prune et Armand sont au parc avec papa. Ils se passent un ballon. Armand a un corps plus rond. Prune a un corps plus mince. Le corps n'est pas une blague. On joue ensemble. Prune ne commente pas le corps. Elle passe le ballon. Armand le rend. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le corps n'est pas une blague.</t>
+          <t>La fontaine du parc chante un filet d'eau. L'eau est claire et un peu froide. Un bateau de bois attend dans le sable. Sa voile blanche est un peu penchée. Un pigeon marche sur le chemin. Le banc a des rayures d'ombre. En ce moment, Raphaël ramasse le bateau. Il attendait dans le sable, Raphaël. Sa voile est penchée. On la redressera après le jeu. Raphaël pose le bateau sur le banc. Aniss arrive avec un ballon. Aniss a un corps plus rond. Raphaël a un corps plus mince. Le corps n'est pas une blague. On joue ensemble. Raphaël ne commente pas le corps. Il passe le ballon. Aniss le rend. À toi. À toi. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le ballon tape le chemin. Pouf. Pouf. Le pigeon s'écarte, puis revient. Le corps n'est pas une blague. Vous jouez. C'est ça. Raphaël vise le banc. Aniss vise le pied de la fontaine. Le ballon reste près de l'eau. Bravo. Vous vous le passez bien. Le bateau nous regarde. Oui. Il attend son tour. Ils posent le ballon. Ils redressent la voile du bateau. Le bois est chaud et un peu rêche. La voile est droite, hein ? Oui. Elle est droite. On le fait avancer. Ils poussent le bateau dans le sable. Le sable fait un sillon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Prune et Armand sont au parc avec papa. Ils se passent un ballon. Armand a un corps plus rond. Prune a un corps plus mince.
-papa|Le corps n'est pas une blague. On joue ensemble.
-narrateur|Prune ne commente pas le corps. Elle passe le ballon. Armand le rend. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le corps n'est pas une blague.</t>
+          <t>narrateur|La fontaine du parc chante un filet d'eau.
+narrateur|L'eau est claire et un peu froide.
+narrateur|Un bateau de bois attend dans le sable.
+narrateur|Sa voile blanche est un peu penchée.
+narrateur|Un pigeon marche sur le chemin.
+narrateur|Le banc a des rayures d'ombre.
+narrateur|En ce moment, Raphaël ramasse le bateau.
+papa|Il attendait dans le sable, Raphaël.
+enfant-m|Sa voile est penchée.
+papa|On la redressera après le jeu.
+narrateur|Raphaël pose le bateau sur le banc.
+narrateur|Aniss arrive avec un ballon.
+narrateur|Aniss a un corps plus rond.
+narrateur|Raphaël a un corps plus mince.
+papa|Le corps n'est pas une blague.
+papa|On joue ensemble.
+narrateur|Raphaël ne commente pas le corps.
+narrateur|Il passe le ballon.
+narrateur|Aniss le rend.
+copain|À toi.
+enfant-m|À toi.
+narrateur|Ils rient du jeu, pas du corps.
+papa|L'amitié ne dépend pas de la forme.
+papa|On joue.
+narrateur|Le ballon tape le chemin.
+narrateur|Pouf. Pouf.
+narrateur|Le pigeon s'écarte, puis revient.
+papa|Le corps n'est pas une blague.
+papa|Vous jouez. C'est ça.
+narrateur|Raphaël vise le banc.
+narrateur|Aniss vise le pied de la fontaine.
+narrateur|Le ballon reste près de l'eau.
+papa|Bravo. Vous vous le passez bien.
+enfant-m|Le bateau nous regarde.
+papa|Oui. Il attend son tour.
+narrateur|Ils posent le ballon.
+narrateur|Ils redressent la voile du bateau.
+narrateur|Le bois est chaud et un peu rêche.
+papa|La voile est droite, hein ?
+enfant-m|Oui. Elle est droite.
+copain|On le fait avancer.
+narrateur|Ils poussent le bateau dans le sable.
+narrateur|Le sable fait un sillon.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Prune joue avec Armand. Que fait-on ?</t>
+          <t>Raphaël joue avec Aniss. Que fait-on ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1554,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Prune joue avec Armand. Que fait-on ?</t>
+          <t>narrateur|Raphaël joue avec Aniss.
+narrateur|Que fait-on ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1583,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Prune a joué avec Armand. Le corps n'était pas une blague.</t>
+          <t>Raphaël a joué avec Aniss. Le corps n'était pas une blague. Bravo, Raphaël. Tu as fait du bon travail. Tu as passé le ballon. Tu as redressé la voile. Le bateau avance encore un peu. Il va vers l'eau. On le garde au bord. L'eau de la fontaine est pour regarder. Il a une belle voile. Elle est droite maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1727,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Prune a joué avec Armand. Le corps n'était pas une blague.</t>
+          <t>narrateur|Raphaël a joué avec Aniss.
+narrateur|Le corps n'était pas une blague.
+papa|Bravo, Raphaël. Tu as fait du bon travail.
+papa|Tu as passé le ballon. Tu as redressé la voile.
+narrateur|Le bateau avance encore un peu.
+enfant-m|Il va vers l'eau.
+papa|On le garde au bord. L'eau de la fontaine est pour regarder.
+copain|Il a une belle voile.
+enfant-m|Elle est droite maintenant.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Prune essuie ses mains.</t>
+          <t>On range le ballon. Papa range le ballon. Raphaël essuie ses mains. Il reste un peu de sable. Tu as fini de jouer ? Oui, papa. Merci. Bravo. Raphaël reprend le bateau. Aniss tient la voile pour qu'elle reste droite. Merci, Aniss. Merci, Raphaël. La fontaine chante encore son filet d'eau.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1903,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Prune essuie ses mains.</t>
+          <t>papa|On range le ballon.
+narrateur|Papa range le ballon.
+narrateur|Raphaël essuie ses mains.
+narrateur|Il reste un peu de sable.
+papa|Tu as fini de jouer ?
+enfant-m|Oui, papa.
+papa|Merci. Bravo.
+narrateur|Raphaël reprend le bateau.
+narrateur|Aniss tient la voile pour qu'elle reste droite.
+enfant-m|Merci, Aniss.
+copain|Merci, Raphaël.
+narrateur|La fontaine chante encore son filet d'eau.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1942,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. Le bateau a avancé. Le corps n'est pas une blague. On joue. Bravo. C'était du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2082,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué. Le bateau a avancé.
+papa|Le corps n'est pas une blague. On joue.
+papa|Bravo. C'était du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.002-05.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-05.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La fontaine du parc chante un filet d'eau. L'eau est claire et un peu froide. Un bateau de bois attend dans le sable. Sa voile blanche est un peu penchée. Un pigeon marche sur le chemin. Le banc a des rayures d'ombre. En ce moment, Raphaël ramasse le bateau. Il attendait dans le sable, Raphaël. Sa voile est penchée. On la redressera après le jeu. Raphaël pose le bateau sur le banc. Aniss arrive avec un ballon. Aniss a un corps plus rond. Raphaël a un corps plus mince. Le corps n'est pas une blague. On joue ensemble. Raphaël ne commente pas le corps. Il passe le ballon. Aniss le rend. À toi. À toi. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le ballon tape le chemin. Pouf. Pouf. Le pigeon s'écarte, puis revient. Le corps n'est pas une blague. Vous jouez. C'est ça. Raphaël vise le banc. Aniss vise le pied de la fontaine. Le ballon reste près de l'eau. Bravo. Vous vous le passez bien. Le bateau nous regarde. Oui. Il attend son tour. Ils posent le ballon. Ils redressent la voile du bateau. Le bois est chaud et un peu rêche. La voile est droite, hein ? Oui. Elle est droite. On le fait avancer. Ils poussent le bateau dans le sable. Le sable fait un sillon.</t>
+          <t>La fontaine du parc chante un filet d'eau. L'eau est claire et un peu froide. Un bateau de bois attend dans le sable. Sa voile blanche est un peu penchée. Un pigeon marche sur le chemin. Le banc a des rayures d'ombre. En ce moment, Raphaël ramasse le bateau. Il attendait dans le sable, Raphaël. Sa voile est penchée. On la redressera après le jeu. Raphaël pose le bateau sur le banc. Aniss arrive avec un ballon. Aniss a un corps plus rond. Raphaël a un corps plus mince. Le corps n'est pas une blague. On joue ensemble. Raphaël ne commente pas le corps. Il passe le ballon. Aniss le rend. À toi. À toi. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le ballon tape le chemin. Pouf. Pouf. Le pigeon s'écarte, puis revient. Le corps n'est pas une blague. Vous jouez. C'est ça. Raphaël vise le banc. Aniss vise le pied de la fontaine. Le ballon reste près de l'eau. Bravo. Vous vous le passez bien. Le bateau nous regarde. Oui. Il attend son tour. Ils posent le ballon. Ils redressent la voile du bateau. Le bois est chaud et un peu rêche. La voile est droite, hein ? Oui. Elle est droite. On le fait avancer. Ils poussent le bateau dans le sable. Le sable fait un sillon. Le sillon est un peu humide près de la fontaine. Raphaël pose deux cailloux. Ce sont des quais. Aniss pose une feuille. C'est une île. Un port. Un bateau. Deux capitaines. On est deux. On est deux. Deux corps différents. Un même jeu. Le filet d'eau continue. Une goutte saute sur le bord. Raphaël l'essuie avec le doigt. L'eau reste dans la fontaine.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1349,24 +1349,45 @@
 papa|L'amitié ne dépend pas de la forme.
 papa|On joue.
 narrateur|Le ballon tape le chemin.
-narrateur|Pouf. Pouf.
+narrateur|Pouf.
+narrateur|Pouf.
 narrateur|Le pigeon s'écarte, puis revient.
 papa|Le corps n'est pas une blague.
-papa|Vous jouez. C'est ça.
+papa|Vous jouez.
+papa|C'est ça.
 narrateur|Raphaël vise le banc.
 narrateur|Aniss vise le pied de la fontaine.
 narrateur|Le ballon reste près de l'eau.
-papa|Bravo. Vous vous le passez bien.
+papa|Bravo.
+papa|Vous vous le passez bien.
 enfant-m|Le bateau nous regarde.
-papa|Oui. Il attend son tour.
+papa|Oui.
+papa|Il attend son tour.
 narrateur|Ils posent le ballon.
 narrateur|Ils redressent la voile du bateau.
 narrateur|Le bois est chaud et un peu rêche.
 papa|La voile est droite, hein ?
-enfant-m|Oui. Elle est droite.
+enfant-m|Oui.
+enfant-m|Elle est droite.
 copain|On le fait avancer.
 narrateur|Ils poussent le bateau dans le sable.
-narrateur|Le sable fait un sillon.</t>
+narrateur|Le sable fait un sillon.
+narrateur|Le sillon est un peu humide près de la fontaine.
+narrateur|Raphaël pose deux cailloux.
+narrateur|Ce sont des quais.
+narrateur|Aniss pose une feuille.
+narrateur|C'est une île.
+papa|Un port.
+papa|Un bateau.
+papa|Deux capitaines.
+enfant-m|On est deux.
+copain|On est deux.
+papa|Deux corps différents.
+papa|Un même jeu.
+narrateur|Le filet d'eau continue.
+narrateur|Une goutte saute sur le bord.
+narrateur|Raphaël l'essuie avec le doigt.
+papa|L'eau reste dans la fontaine.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1729,11 +1750,14 @@
         <is>
           <t>narrateur|Raphaël a joué avec Aniss.
 narrateur|Le corps n'était pas une blague.
-papa|Bravo, Raphaël. Tu as fait du bon travail.
-papa|Tu as passé le ballon. Tu as redressé la voile.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as passé le ballon.
+papa|Tu as redressé la voile.
 narrateur|Le bateau avance encore un peu.
 enfant-m|Il va vers l'eau.
-papa|On le garde au bord. L'eau de la fontaine est pour regarder.
+papa|On le garde au bord.
+papa|L'eau de la fontaine est pour regarder.
 copain|Il a une belle voile.
 enfant-m|Elle est droite maintenant.</t>
         </is>
@@ -1909,7 +1933,8 @@
 narrateur|Il reste un peu de sable.
 papa|Tu as fini de jouer ?
 enfant-m|Oui, papa.
-papa|Merci. Bravo.
+papa|Merci.
+papa|Bravo.
 narrateur|Raphaël reprend le bateau.
 narrateur|Aniss tient la voile pour qu'elle reste droite.
 enfant-m|Merci, Aniss.
@@ -2082,9 +2107,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a joué. Le bateau a avancé.
-papa|Le corps n'est pas une blague. On joue.
-papa|Bravo. C'était du bon travail.
+          <t>enfant-m|On a joué.
+enfant-m|Le bateau a avancé.
+papa|Le corps n'est pas une blague.
+papa|On joue.
+papa|Bravo.
+papa|C'était du bon travail.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2107,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2150,6 +2178,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.002-05.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le bateau dans le sable</t>
+          <t>La cabane de draps de Raphaël</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un bateau de bois attend dans le sable, près de la fontaine. Raphaël et Aniss se passent un ballon. Le corps n'est pas une blague. Ils jouent ensemble.</t>
+          <t>Raphaël veut une cabane avec le drap qui sent le soleil. Aniss arrive. Le corps n'est pas une blague. Le drap est trop court. Ils ajoutent un torchon et s'installent dedans.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La fontaine du parc chante un filet d'eau. L'eau est claire et un peu froide. Un bateau de bois attend dans le sable. Sa voile blanche est un peu penchée. Un pigeon marche sur le chemin. Le banc a des rayures d'ombre. En ce moment, Raphaël ramasse le bateau. Il attendait dans le sable, Raphaël. Sa voile est penchée. On la redressera après le jeu. Raphaël pose le bateau sur le banc. Aniss arrive avec un ballon. Aniss a un corps plus rond. Raphaël a un corps plus mince. Le corps n'est pas une blague. On joue ensemble. Raphaël ne commente pas le corps. Il passe le ballon. Aniss le rend. À toi. À toi. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le ballon tape le chemin. Pouf. Pouf. Le pigeon s'écarte, puis revient. Le corps n'est pas une blague. Vous jouez. C'est ça. Raphaël vise le banc. Aniss vise le pied de la fontaine. Le ballon reste près de l'eau. Bravo. Vous vous le passez bien. Le bateau nous regarde. Oui. Il attend son tour. Ils posent le ballon. Ils redressent la voile du bateau. Le bois est chaud et un peu rêche. La voile est droite, hein ? Oui. Elle est droite. On le fait avancer. Ils poussent le bateau dans le sable. Le sable fait un sillon. Le sillon est un peu humide près de la fontaine. Raphaël pose deux cailloux. Ce sont des quais. Aniss pose une feuille. C'est une île. Un port. Un bateau. Deux capitaines. On est deux. On est deux. Deux corps différents. Un même jeu. Le filet d'eau continue. Une goutte saute sur le bord. Raphaël l'essuie avec le doigt. L'eau reste dans la fontaine.</t>
+          <t>Un drap sent encore le fil et le soleil. Il sèche sur le dossier d'une chaise. Une pince à linge tient un coin. La pince est en bois, un peu ronde. Un rai de poussière traverse le salon. L'horloge fait un tic lent. Une mouche se pose sur la vitre. Le tapis garde un carré de soleil. Tu as senti le drap, Raphaël ? Il sent dehors. Oui. Le soleil l'a séché. En ce moment, Raphaël tire deux chaises. Les pieds des chaises râpent le bois. Je veux une cabane. Avec le drap. Au milieu du salon ? Oui. Aniss arrive. Il a encore une chaussette un peu tordue. Aniss a un corps plus rond. Raphaël a un corps plus mince. Raphaël ne commente pas le corps. Le corps n'est pas une blague. On joue. Aniss, tu tiens la chaise ? Je la tiens. Ils jettent le drap par-dessus. Le drap tombe en biais. Le drap est trop court. Il y a un trou. On cherche un torchon. Le torchon sent encore la vaisselle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Prune et Armand sont au parc avec papa. Ils se passent un ballon. Armand a un &lt;emphasis level="moderate"&gt;corps&lt;/emphasis&gt; plus rond. Prune a un corps plus mince. Papa dit : le corps n'est pas une blague. On joue ensemble. Prune ne commente pas le corps. Elle passe le ballon. Armand le rend. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le corps n'est pas une blague.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un drap sent encore le fil et le soleil. Il sèche sur le dossier d'une chaise. Une pince à linge tient un coin. La pince est en bois, un peu ronde. Un rai de poussière traverse le salon. L'horloge fait un tic lent. Une mouche se pose sur la vitre. Le tapis garde un carré de soleil. Tu as senti le drap, Raphaël ? Il sent dehors. Oui. Le soleil l'a séché. En ce moment, Raphaël tire deux chaises. Les pieds des chaises râpent le bois. Je veux une cabane. Avec le drap. Au milieu du salon ? Oui. Aniss arrive. Il a encore une chaussette un peu tordue. Aniss a un corps plus rond. Raphaël a un corps plus mince. Raphaël ne commente pas le corps. Le corps n'est pas une blague. On joue. Aniss, tu tiens la chaise ? Je la tiens. Ils jettent le drap par-dessus. Le drap tombe en biais. Le drap est trop court. Il y a un trou. On cherche un torchon. Le torchon sent encore la vaisselle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,70 +1324,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La fontaine du parc chante un filet d'eau.
-narrateur|L'eau est claire et un peu froide.
-narrateur|Un bateau de bois attend dans le sable.
-narrateur|Sa voile blanche est un peu penchée.
-narrateur|Un pigeon marche sur le chemin.
-narrateur|Le banc a des rayures d'ombre.
-narrateur|En ce moment, Raphaël ramasse le bateau.
-papa|Il attendait dans le sable, Raphaël.
-enfant-m|Sa voile est penchée.
-papa|On la redressera après le jeu.
-narrateur|Raphaël pose le bateau sur le banc.
-narrateur|Aniss arrive avec un ballon.
+          <t>narrateur|Un drap sent encore le fil et le soleil.
+narrateur|Il sèche sur le dossier d'une chaise.
+narrateur|Une pince à linge tient un coin.
+narrateur|La pince est en bois, un peu ronde.
+narrateur|Un rai de poussière traverse le salon.
+narrateur|L'horloge fait un tic lent.
+narrateur|Une mouche se pose sur la vitre.
+narrateur|Le tapis garde un carré de soleil.
+papa|Tu as senti le drap, Raphaël ?
+enfant-m|Il sent dehors.
+papa|Oui.
+papa|Le soleil l'a séché.
+narrateur|En ce moment, Raphaël tire deux chaises.
+narrateur|Les pieds des chaises râpent le bois.
+enfant-m|Je veux une cabane.
+enfant-m|Avec le drap.
+papa|Au milieu du salon ?
+enfant-m|Oui.
+narrateur|Aniss arrive.
+narrateur|Il a encore une chaussette un peu tordue.
 narrateur|Aniss a un corps plus rond.
 narrateur|Raphaël a un corps plus mince.
+narrateur|Raphaël ne commente pas le corps.
 papa|Le corps n'est pas une blague.
-papa|On joue ensemble.
-narrateur|Raphaël ne commente pas le corps.
-narrateur|Il passe le ballon.
-narrateur|Aniss le rend.
-copain|À toi.
-enfant-m|À toi.
-narrateur|Ils rient du jeu, pas du corps.
-papa|L'amitié ne dépend pas de la forme.
 papa|On joue.
-narrateur|Le ballon tape le chemin.
-narrateur|Pouf.
-narrateur|Pouf.
-narrateur|Le pigeon s'écarte, puis revient.
-papa|Le corps n'est pas une blague.
-papa|Vous jouez.
-papa|C'est ça.
-narrateur|Raphaël vise le banc.
-narrateur|Aniss vise le pied de la fontaine.
-narrateur|Le ballon reste près de l'eau.
-papa|Bravo.
-papa|Vous vous le passez bien.
-enfant-m|Le bateau nous regarde.
-papa|Oui.
-papa|Il attend son tour.
-narrateur|Ils posent le ballon.
-narrateur|Ils redressent la voile du bateau.
-narrateur|Le bois est chaud et un peu rêche.
-papa|La voile est droite, hein ?
-enfant-m|Oui.
-enfant-m|Elle est droite.
-copain|On le fait avancer.
-narrateur|Ils poussent le bateau dans le sable.
-narrateur|Le sable fait un sillon.
-narrateur|Le sillon est un peu humide près de la fontaine.
-narrateur|Raphaël pose deux cailloux.
-narrateur|Ce sont des quais.
-narrateur|Aniss pose une feuille.
-narrateur|C'est une île.
-papa|Un port.
-papa|Un bateau.
-papa|Deux capitaines.
-enfant-m|On est deux.
-copain|On est deux.
-papa|Deux corps différents.
-papa|Un même jeu.
-narrateur|Le filet d'eau continue.
-narrateur|Une goutte saute sur le bord.
-narrateur|Raphaël l'essuie avec le doigt.
-papa|L'eau reste dans la fontaine.</t>
+enfant-m|Aniss, tu tiens la chaise ?
+copain|Je la tiens.
+narrateur|Ils jettent le drap par-dessus.
+narrateur|Le drap tombe en biais.
+narrateur|Le drap est trop court.
+enfant-m|Il y a un trou.
+papa|On cherche un torchon.
+narrateur|Le torchon sent encore la vaisselle.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1419,12 +1388,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Raphaël joue avec Aniss. Que fait-on ?</t>
+          <t>Le corps n'est pas une blague. Que fait-on ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Prune joue avec Armand. Que fait-on ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le corps n'est pas une blague. Que fait-on ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1439,7 +1408,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>jouer | pas une blague | ensemble</t>
+          <t>jouer | on joue | pas une blague | pas blague | la cabane</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1454,7 +1423,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le corps n'est pas une blague. Que fait-on ?</t>
+          <t>On joue. Le corps n'est pas une blague. Que fait-on ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1575,11 +1544,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël joue avec Aniss.
+          <t>narrateur|Le corps n'est pas une blague.
 narrateur|Que fait-on ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1604,12 +1572,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a joué avec Aniss. Le corps n'était pas une blague. Bravo, Raphaël. Tu as fait du bon travail. Tu as passé le ballon. Tu as redressé la voile. Le bateau avance encore un peu. Il va vers l'eau. On le garde au bord. L'eau de la fontaine est pour regarder. Il a une belle voile. Elle est droite maintenant.</t>
+          <t>Papa tend un torchon à carreaux. Raphaël le pince au bord du drap. Le trou se ferme. On entre ? On entre. Ils se glissent dessous. La lumière devient jaune. Le drap sent encore le soleil. On entend l'horloge, plus loin. On est dedans. C'est chaud. Deux biscuits, pour les capitaines. Papa passe les biscuits sous le bord. Ça croque tout doux. Une miette tombe sur le tapis. Bravo, Raphaël. Tu as fermé le trou. Vous jouez. L'amitié ne dépend pas de la forme. Une chaise glisse un peu. Attends. Aniss la recale. La cabane tient. Elle est solide.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Prune a joué avec Armand. Le &lt;emphasis level="moderate"&gt;corps&lt;/emphasis&gt; n'était pas une blague.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa tend un torchon à carreaux. Raphaël le pince au bord du drap. Le trou se ferme. On entre ? On entre. Ils se glissent dessous. La lumière devient jaune. Le drap sent encore le soleil. On entend l'horloge, plus loin. On est dedans. C'est chaud. Deux biscuits, pour les capitaines. Papa passe les biscuits sous le bord. Ça croque tout doux. Une miette tombe sur le tapis. Bravo, Raphaël. Tu as fermé le trou. Vous jouez. L'amitié ne dépend pas de la forme. Une chaise glisse un peu. Attends. Aniss la recale. La cabane tient. Elle est solide.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,21 +1716,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a joué avec Aniss.
-narrateur|Le corps n'était pas une blague.
+          <t>narrateur|Papa tend un torchon à carreaux.
+narrateur|Raphaël le pince au bord du drap.
+narrateur|Le trou se ferme.
+copain|On entre ?
+enfant-m|On entre.
+narrateur|Ils se glissent dessous.
+narrateur|La lumière devient jaune.
+narrateur|Le drap sent encore le soleil.
+narrateur|On entend l'horloge, plus loin.
+enfant-m|On est dedans.
+copain|C'est chaud.
+papa|Deux biscuits, pour les capitaines.
+narrateur|Papa passe les biscuits sous le bord.
+narrateur|Ça croque tout doux.
+narrateur|Une miette tombe sur le tapis.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
-papa|Tu as passé le ballon.
-papa|Tu as redressé la voile.
-narrateur|Le bateau avance encore un peu.
-enfant-m|Il va vers l'eau.
-papa|On le garde au bord.
-papa|L'eau de la fontaine est pour regarder.
-copain|Il a une belle voile.
-enfant-m|Elle est droite maintenant.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Tu as fermé le trou.
+papa|Vous jouez.
+papa|L'amitié ne dépend pas de la forme.
+narrateur|Une chaise glisse un peu.
+enfant-m|Attends.
+narrateur|Aniss la recale.
+narrateur|La cabane tient.
+enfant-m|Elle est solide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,12 +1766,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On range le ballon. Papa range le ballon. Raphaël essuie ses mains. Il reste un peu de sable. Tu as fini de jouer ? Oui, papa. Merci. Bravo. Raphaël reprend le bateau. Aniss tient la voile pour qu'elle reste droite. Merci, Aniss. Merci, Raphaël. La fontaine chante encore son filet d'eau.</t>
+          <t>On reste encore un peu ? Oui. Un peu. L'horloge tic plus loin. La mouche a quitté la vitre. Tu as fini tes biscuits ? Oui, papa. Ils sortent à reculons. Le salon redevient grand. Le rai de poussière est encore là. Raphaël plie le drap. Aniss plie le torchon. Merci, Aniss. Merci, Raphaël. Le drap sent encore le soleil. La pince à linge reste sur la chaise.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le ballon. Prune essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On reste encore un peu ? Oui. Un peu. L'horloge tic plus loin. La mouche a quitté la vitre. Tu as fini tes biscuits ? Oui, papa. Ils sortent à reculons. Le salon redevient grand. Le rai de poussière est encore là. Raphaël plie le drap. Aniss plie le torchon. Merci, Aniss. Merci, Raphaël. Le drap sent encore le soleil. La pince à linge reste sur la chaise.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,22 +1906,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>papa|On range le ballon.
-narrateur|Papa range le ballon.
-narrateur|Raphaël essuie ses mains.
-narrateur|Il reste un peu de sable.
-papa|Tu as fini de jouer ?
+          <t>papa|On reste encore un peu ?
+enfant-m|Oui.
+copain|Un peu.
+narrateur|L'horloge tic plus loin.
+narrateur|La mouche a quitté la vitre.
+papa|Tu as fini tes biscuits ?
 enfant-m|Oui, papa.
-papa|Merci.
-papa|Bravo.
-narrateur|Raphaël reprend le bateau.
-narrateur|Aniss tient la voile pour qu'elle reste droite.
+narrateur|Ils sortent à reculons.
+narrateur|Le salon redevient grand.
+narrateur|Le rai de poussière est encore là.
+narrateur|Raphaël plie le drap.
+narrateur|Aniss plie le torchon.
 enfant-m|Merci, Aniss.
 copain|Merci, Raphaël.
-narrateur|La fontaine chante encore son filet d'eau.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+papa|Le drap sent encore le soleil.
+narrateur|La pince à linge reste sur la chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1967,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a joué. Le bateau a avancé. Le corps n'est pas une blague. On joue. Bravo. C'était du bon travail. L'histoire est finie.</t>
+          <t>On a fait la cabane. On a mangé dedans. Vous avez joué. Le drap garde un peu de jaune. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a fait la cabane. On a mangé dedans. Vous avez joué. Le drap garde un peu de jaune. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2028,14 +2009,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2107,16 +2088,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a joué.
-enfant-m|Le bateau a avancé.
-papa|Le corps n'est pas une blague.
-papa|On joue.
-papa|Bravo.
-papa|C'était du bon travail.
+          <t>enfant-m|On a fait la cabane.
+copain|On a mangé dedans.
+papa|Vous avez joué.
+narrateur|Le drap garde un peu de jaune.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2135,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2208,6 +2186,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.002-05.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-05.xlsx
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a fait la cabane. On a mangé dedans. Vous avez joué. Le drap garde un peu de jaune. L'histoire est finie.</t>
+          <t>On a fait la cabane. On a mangé dedans. Vous avez joué. Le drap garde un peu de jaune.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a fait la cabane. On a mangé dedans. Vous avez joué. Le drap garde un peu de jaune. L'histoire est finie.</t>
+          <t>On a fait la cabane. On a mangé dedans. Vous avez joué. Le drap garde un peu de jaune.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2091,8 +2091,7 @@
           <t>enfant-m|On a fait la cabane.
 copain|On a mangé dedans.
 papa|Vous avez joué.
-narrateur|Le drap garde un peu de jaune.
-narrateur|L'histoire est finie.</t>
+narrateur|Le drap garde un peu de jaune.</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2191,6 +2190,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.002-05.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>salon l'après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prune, Armand, papa</t>
+          <t>Raphaël, Aniss, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.002-05.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon l'après-midi</t>
+          <t>salon l'après-midi, drap, pince, chaise</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Raphaël, Aniss, papa</t>
+          <t>Raphaël, Aniss, papa, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Raphaël veut une cabane avec le drap qui sent le soleil. Aniss arrive. Le corps n'est pas une blague. Le drap est trop court. Ils ajoutent un torchon et s'installent dedans.</t>
+          <t>Un rai de poussière traverse le salon. Sur le bois, un éclat de chaise brille. Raphaël veut une cabane, maintenant, avec le drap. Aniss arrive. Le drap gonfle. Un rire commence. Aniss se tait. Le drap trop court. Raphaël refuse de foncer. Ils tiennent les chaises, à deux. Merci vécu. Une chaise trop vite. L'éclat de chaise tient sur le bois.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un drap sent encore le fil et le soleil. Il sèche sur le dossier d'une chaise. Une pince à linge tient un coin. La pince est en bois, un peu ronde. Un rai de poussière traverse le salon. L'horloge fait un tic lent. Une mouche se pose sur la vitre. Le tapis garde un carré de soleil. Tu as senti le drap, Raphaël ? Il sent dehors. Oui. Le soleil l'a séché. En ce moment, Raphaël tire deux chaises. Les pieds des chaises râpent le bois. Je veux une cabane. Avec le drap. Au milieu du salon ? Oui. Aniss arrive. Il a encore une chaussette un peu tordue. Aniss a un corps plus rond. Raphaël a un corps plus mince. Raphaël ne commente pas le corps. Le corps n'est pas une blague. On joue. Aniss, tu tiens la chaise ? Je la tiens. Ils jettent le drap par-dessus. Le drap tombe en biais. Le drap est trop court. Il y a un trou. On cherche un torchon. Le torchon sent encore la vaisselle.</t>
+          <t>Un rai de poussière traverse le salon. Il brille dans le carré de soleil. Il brille, papa ! Tu le vois, près du tapis ? Oui, un trait clair. L'horloge fait un tic lent. Je l'entends, maman. Elle tic, près de la vitre ? Oui, maman. Un drap sent le fil, un peu chaud. Il sèche sur le dossier d'une chaise. Une pince de bois tient un coin. Elle pince le drap. La pince est en bois, Raphaël ? Oui, un peu ronde. Sur le bois, un éclat de chaise brille. Il brille, papa. Tu le vois, sur la chaise ? Oui, un petit point. Le tapis garde un carré de soleil. Tes pieds sont sur le tapis ? Oui, maman. Une mouche se pose sur la vitre. Elle est là. Près du soleil ? Oui. Je veux une cabane, maintenant ! Avec le drap ? Oui, au milieu. Au milieu du salon ? Oui, maman. En ce moment, Raphaël tire deux chaises. Les pieds des chaises râpent le bois. Elles font du bruit. Tu les poses, Raphaël ? Oui, papa. Aniss arrive près du tapis. Il a une chaussette un peu tordue. Aniss ! J'arrive. Tu tiens la chaise, maintenant ! Ils jettent le drap par-dessus. Le drap tombe en biais. Aniss se glisse dessous, un peu. Le drap gonfle sur ses épaules. Ça gonfle drôle ! Un rire commence dans la bouche de Raphaël. Aniss ne dit rien. Le sourire d'Aniss disparaît. Non. Aniss recule vers la vitre. Oh. Raphaël jette le drap trop vite, tout seul. Le drap est trop court. Il y a un trou ! Oh. L'éclat de chaise tremble, puis tient. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Aniss, Raphaël ? Oui, papa. Tes mains tiennent le drap ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un drap sent encore le fil et le soleil. Il sèche sur le dossier d'une chaise. Une pince à linge tient un coin. La pince est en bois, un peu ronde. Un rai de poussière traverse le salon. L'horloge fait un tic lent. Une mouche se pose sur la vitre. Le tapis garde un carré de soleil. Tu as senti le drap, Raphaël ? Il sent dehors. Oui. Le soleil l'a séché. En ce moment, Raphaël tire deux chaises. Les pieds des chaises râpent le bois. Je veux une cabane. Avec le drap. Au milieu du salon ? Oui. Aniss arrive. Il a encore une chaussette un peu tordue. Aniss a un corps plus rond. Raphaël a un corps plus mince. Raphaël ne commente pas le corps. Le corps n'est pas une blague. On joue. Aniss, tu tiens la chaise ? Je la tiens. Ils jettent le drap par-dessus. Le drap tombe en biais. Le drap est trop court. Il y a un trou. On cherche un torchon. Le torchon sent encore la vaisselle.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un rai de poussière traverse le salon. Il brille dans le carré de soleil. Il brille, papa ! Tu le vois, près du tapis ? Oui, un trait clair. L'horloge fait un tic lent. Je l'entends, maman. Elle tic, près de la vitre ? Oui, maman. Un drap sent le fil, un peu chaud. Il sèche sur le dossier d'une chaise. Une pince de bois tient un coin. Elle pince le drap. La pince est en bois, Raphaël ? Oui, un peu ronde. Sur le bois, un &lt;emphasis level="moderate"&gt;éclat de chaise&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur la chaise ? Oui, un petit point. Le tapis garde un carré de soleil. Tes pieds sont sur le tapis ? Oui, maman. Une mouche se pose sur la vitre. Elle est là. Près du soleil ? Oui. Je veux une cabane, maintenant ! Avec le drap ? Oui, au milieu. Au milieu du salon ? Oui, maman. En ce moment, Raphaël tire deux chaises. Les pieds des chaises râpent le bois. Elles font du bruit. Tu les poses, Raphaël ? Oui, papa. Aniss arrive près du tapis. Il a une chaussette un peu tordue. Aniss ! J'arrive. Tu tiens la chaise, maintenant ! Ils jettent le drap par-dessus. Le drap tombe en biais. Aniss se glisse dessous, un peu. Le drap gonfle sur ses épaules. Ça gonfle drôle ! Un rire commence dans la bouche de Raphaël. Aniss ne dit rien. Le sourire d'Aniss disparaît. Non. Aniss recule vers la vitre. Oh. Raphaël jette le drap trop vite, tout seul. Le drap est trop court. Il y a un trou ! Oh. L'éclat de chaise tremble, puis tient. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Aniss, Raphaël ? Oui, papa. Tes mains tiennent le drap ? Un peu, maman.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Prune et Armand sont au parc avec papa. Ils se passent un ballon. Armand a un &lt;emphasis&gt;corps&lt;/emphasis&gt; plus rond. Prune a un corps plus mince. Papa dit : le corps n'est pas une blague. On joue ensemble. Prune ne commente pas le corps. Elle passe le ballon. Armand le rend. Ils rient du jeu, pas du corps. L'amitié ne dépend pas de la forme. On joue. Le corps n'est pas une blague. [pause]</t>
+          <t>Un rai de poussière traverse le salon. Il brille dans le carré de soleil. Il brille, papa ! Tu le vois, près du tapis ? Oui, un trait clair. L'horloge fait un tic lent. Je l'entends, maman. Elle tic, près de la vitre ? Oui, maman. Un drap sent le fil, un peu chaud. Il sèche sur le dossier d'une chaise. Une pince de bois tient un coin. Elle pince le drap. La pince est en bois, Raphaël ? Oui, un peu ronde. Sur le bois, un &lt;emphasis&gt;éclat de chaise&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur la chaise ? Oui, un petit point. Le tapis garde un carré de soleil. Tes pieds sont sur le tapis ? Oui, maman. Une mouche se pose sur la vitre. Elle est là. Près du soleil ? Oui. Je veux une cabane, maintenant ! Avec le drap ? Oui, au milieu. Au milieu du salon ? Oui, maman. En ce moment, Raphaël tire deux chaises. Les pieds des chaises râpent le bois. Elles font du bruit. Tu les poses, Raphaël ? Oui, papa. Aniss arrive près du tapis. Il a une chaussette un peu tordue. Aniss ! J'arrive. Tu tiens la chaise, maintenant ! Ils jettent le drap par-dessus. Le drap tombe en biais. Aniss se glisse dessous, un peu. Le drap gonfle sur ses épaules. Ça gonfle drôle ! Un rire commence dans la bouche de Raphaël. Aniss ne dit rien. Le sourire d'Aniss disparaît. Non. Aniss recule vers la vitre. Oh. Raphaël jette le drap trop vite, tout seul. Le drap est trop court. Il y a un trou ! Oh. L'éclat de chaise tremble, puis tient. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Aniss, Raphaël ? Oui, papa. Tes mains tiennent le drap ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1.12</v>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>éclat de chaise</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,47 +1321,83 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_la_cabane_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un drap sent encore le fil et le soleil.
+          <t>narrateur|Un rai de poussière traverse le salon.
+narrateur|Il brille dans le carré de soleil.
+enfant-m|Il brille, papa !
+papa|Tu le vois, près du tapis ?
+enfant-m|Oui, un trait clair.
+narrateur|L'horloge fait un tic lent.
+enfant-m|Je l'entends, maman.
+maman|Elle tic, près de la vitre ?
+enfant-m|Oui, maman.
+narrateur|Un drap sent le fil, un peu chaud.
 narrateur|Il sèche sur le dossier d'une chaise.
-narrateur|Une pince à linge tient un coin.
-narrateur|La pince est en bois, un peu ronde.
-narrateur|Un rai de poussière traverse le salon.
-narrateur|L'horloge fait un tic lent.
+narrateur|Une pince de bois tient un coin.
+enfant-m|Elle pince le drap.
+papa|La pince est en bois, Raphaël ?
+enfant-m|Oui, un peu ronde.
+narrateur|Sur le bois, un éclat de chaise brille.
+enfant-m|Il brille, papa.
+papa|Tu le vois, sur la chaise ?
+enfant-m|Oui, un petit point.
+narrateur|Le tapis garde un carré de soleil.
+maman|Tes pieds sont sur le tapis ?
+enfant-m|Oui, maman.
 narrateur|Une mouche se pose sur la vitre.
-narrateur|Le tapis garde un carré de soleil.
-papa|Tu as senti le drap, Raphaël ?
-enfant-m|Il sent dehors.
-papa|Oui.
-papa|Le soleil l'a séché.
+enfant-m|Elle est là.
+maman|Près du soleil ?
+enfant-m|Oui.
+enfant-m|Je veux une cabane, maintenant !
+papa|Avec le drap ?
+enfant-m|Oui, au milieu.
+maman|Au milieu du salon ?
+enfant-m|Oui, maman.
 narrateur|En ce moment, Raphaël tire deux chaises.
 narrateur|Les pieds des chaises râpent le bois.
-enfant-m|Je veux une cabane.
-enfant-m|Avec le drap.
-papa|Au milieu du salon ?
-enfant-m|Oui.
-narrateur|Aniss arrive.
-narrateur|Il a encore une chaussette un peu tordue.
-narrateur|Aniss a un corps plus rond.
-narrateur|Raphaël a un corps plus mince.
-narrateur|Raphaël ne commente pas le corps.
-papa|Le corps n'est pas une blague.
-papa|On joue.
-enfant-m|Aniss, tu tiens la chaise ?
-copain|Je la tiens.
+enfant-m|Elles font du bruit.
+papa|Tu les poses, Raphaël ?
+enfant-m|Oui, papa.
+narrateur|Aniss arrive près du tapis.
+narrateur|Il a une chaussette un peu tordue.
+enfant-m|Aniss !
+copain|J'arrive.
+enfant-m|Tu tiens la chaise, maintenant !
 narrateur|Ils jettent le drap par-dessus.
 narrateur|Le drap tombe en biais.
+narrateur|Aniss se glisse dessous, un peu.
+narrateur|Le drap gonfle sur ses épaules.
+enfant-m|Ça gonfle drôle !
+narrateur|Un rire commence dans la bouche de Raphaël.
+narrateur|Aniss ne dit rien.
+narrateur|Le sourire d'Aniss disparaît.
+copain|Non.
+narrateur|Aniss recule vers la vitre.
+enfant-m|Oh.
+narrateur|Raphaël jette le drap trop vite, tout seul.
 narrateur|Le drap est trop court.
-enfant-m|Il y a un trou.
-papa|On cherche un torchon.
-narrateur|Le torchon sent encore la vaisselle.</t>
+enfant-m|Il y a un trou !
+copain|Oh.
+narrateur|L'éclat de chaise tremble, puis tient.
+narrateur|Le sourire de Raphaël disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu vois Aniss, Raphaël ?
+enfant-m|Oui, papa.
+maman|Tes mains tiennent le drap ?
+enfant-m|Un peu, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>horloge,drap</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1429,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Le corps n'est pas une blague. Que fait-on ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;corps&lt;/emphasis&gt; n'est pas une blague. Que fait-on ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Prune joue avec Armand. Que fait-on ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Le &lt;emphasis&gt;corps&lt;/emphasis&gt; n'est pas une blague. Que fait-on ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1461,18 +1497,18 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1487,34 +1523,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1523,23 +1563,23 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=on_joue_on_ne_rit_pas_du_corps; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1572,17 +1612,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Papa tend un torchon à carreaux. Raphaël le pince au bord du drap. Le trou se ferme. On entre ? On entre. Ils se glissent dessous. La lumière devient jaune. Le drap sent encore le soleil. On entend l'horloge, plus loin. On est dedans. C'est chaud. Deux biscuits, pour les capitaines. Papa passe les biscuits sous le bord. Ça croque tout doux. Une miette tombe sur le tapis. Bravo, Raphaël. Tu as fermé le trou. Vous jouez. L'amitié ne dépend pas de la forme. Une chaise glisse un peu. Attends. Aniss la recale. La cabane tient. Elle est solide.</t>
+          <t>Raphaël veut le drap, tout de suite. Je le jette, maintenant ! Il avance trop vite vers Aniss. Les mots se bousculent dans sa bouche. Non. Aniss reste près de la vitre. Oh. Le sourire ne revient pas. Raphaël refuse de foncer. Il referme la bouche. Personne ne parle. Il observe les chaises, un instant. Il écoute le tic de l'horloge. Tu veux la cabane avec Aniss ? Papa reste à la même hauteur. Tu tiens la chaise ? Aniss ne dit rien, d'abord. Il pose les mains sur le bois. Je la tiens. D'accord. Merci, Raphaël. Papa a vu les deux, près du drap. Le drap est chaud, sous les doigts. Il sent le soleil. Ils rapprochent les chaises, sans se presser. Raphaël pince un coin, avec la pince. Le trou se ferme, cette fois. Il tient ! Oui. Tu le vois, le toit ? Oui, papa. On entre, Raphaël ? On entre. On entre. Ils se glissent dessous. La lumière devient jaune. On est dedans. C'est chaud. Deux biscuits, pour vous. Papa passe les biscuits sous le bord. Ça croque, un peu. Une miette tombe sur le tapis. La miette est sur le tapis ? Oui, maman. Le ventre de Raphaël se desserre. Les épaules se relèvent un peu. On reste sous le drap ? Oui. Tes mains sont au chaud ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Papa tend un torchon à carreaux. Raphaël le pince au bord du drap. Le trou se ferme. On entre ? On entre. Ils se glissent dessous. La lumière devient jaune. Le drap sent encore le soleil. On entend l'horloge, plus loin. On est dedans. C'est chaud. Deux biscuits, pour les capitaines. Papa passe les biscuits sous le bord. Ça croque tout doux. Une miette tombe sur le tapis. Bravo, Raphaël. Tu as fermé le trou. Vous jouez. L'amitié ne dépend pas de la forme. Une chaise glisse un peu. Attends. Aniss la recale. La cabane tient. Elle est solide.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël veut le &lt;emphasis level="moderate"&gt;drap&lt;/emphasis&gt;, tout de suite. Je le jette, maintenant ! Il avance trop vite vers Aniss. Les mots se bousculent dans sa bouche. Non. Aniss reste près de la vitre. Oh. Le sourire ne revient pas. Raphaël refuse de foncer. Il referme la bouche. Personne ne parle. Il observe les chaises, un instant. Il écoute le tic de l'horloge. Tu veux la cabane avec Aniss ? Papa reste à la même hauteur. Tu tiens la chaise ? Aniss ne dit rien, d'abord. Il pose les mains sur le bois. Je la tiens. D'accord. Merci, Raphaël. Papa a vu les deux, près du drap. Le drap est chaud, sous les doigts. Il sent le soleil. Ils rapprochent les chaises, sans se presser. Raphaël pince un coin, avec la pince. Le trou se ferme, cette fois. Il tient ! Oui. Tu le vois, le toit ? Oui, papa. On entre, Raphaël ? On entre. On entre. Ils se glissent dessous. La lumière devient jaune. On est dedans. C'est chaud. Deux biscuits, pour vous. Papa passe les biscuits sous le bord. Ça croque, un peu. Une miette tombe sur le tapis. La miette est sur le tapis ? Oui, maman. Le ventre de Raphaël se desserre. Les épaules se relèvent un peu. On reste sous le drap ? Oui. Tes mains sont au chaud ? Un peu, maman.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Prune a joué avec Armand. Le &lt;emphasis&gt;corps&lt;/emphasis&gt; n'était pas une blague. [pause]</t>
+          <t>Raphaël veut le &lt;emphasis&gt;drap&lt;/emphasis&gt;, tout de suite. Je le jette, maintenant ! Il avance trop vite vers Aniss. Les mots se bousculent dans sa bouche. Non. Aniss reste près de la vitre. Oh. Le sourire ne revient pas. Raphaël refuse de foncer. Il referme la bouche. Personne ne parle. Il observe les chaises, un instant. Il écoute le tic de l'horloge. Tu veux la cabane avec Aniss ? Papa reste à la même hauteur. Tu tiens la chaise ? Aniss ne dit rien, d'abord. Il pose les mains sur le bois. Je la tiens. D'accord. Merci, Raphaël. Papa a vu les deux, près du drap. Le drap est chaud, sous les doigts. Il sent le soleil. Ils rapprochent les chaises, sans se presser. Raphaël pince un coin, avec la pince. Le trou se ferme, cette fois. Il tient ! Oui. Tu le vois, le toit ? Oui, papa. On entre, Raphaël ? On entre. On entre. Ils se glissent dessous. La lumière devient jaune. On est dedans. C'est chaud. Deux biscuits, pour vous. Papa passe les biscuits sous le bord. Ça croque, un peu. Une miette tombe sur le tapis. La miette est sur le tapis ? Oui, maman. Le ventre de Raphaël se desserre. Les épaules se relèvent un peu. On reste sous le drap ? Oui. Tes mains sont au chaud ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1629,7 +1669,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1637,10 +1677,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1663,30 +1703,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>drap</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1695,10 +1735,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1711,35 +1751,66 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=ils_tiennent_les_chaises_a_deux; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Papa tend un torchon à carreaux.
-narrateur|Raphaël le pince au bord du drap.
-narrateur|Le trou se ferme.
-copain|On entre ?
+          <t>narrateur|Raphaël veut le drap, tout de suite.
+enfant-m|Je le jette, maintenant !
+narrateur|Il avance trop vite vers Aniss.
+narrateur|Les mots se bousculent dans sa bouche.
+copain|Non.
+narrateur|Aniss reste près de la vitre.
+enfant-m|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Raphaël refuse de foncer.
+narrateur|Il referme la bouche.
+narrateur|Personne ne parle.
+narrateur|Il observe les chaises, un instant.
+narrateur|Il écoute le tic de l'horloge.
+papa|Tu veux la cabane avec Aniss ?
+narrateur|Papa reste à la même hauteur.
+enfant-m|Tu tiens la chaise ?
+narrateur|Aniss ne dit rien, d'abord.
+narrateur|Il pose les mains sur le bois.
+copain|Je la tiens.
+enfant-m|D'accord.
+papa|Merci, Raphaël.
+narrateur|Papa a vu les deux, près du drap.
+maman|Le drap est chaud, sous les doigts.
+enfant-m|Il sent le soleil.
+narrateur|Ils rapprochent les chaises, sans se presser.
+narrateur|Raphaël pince un coin, avec la pince.
+narrateur|Le trou se ferme, cette fois.
+enfant-m|Il tient !
+copain|Oui.
+papa|Tu le vois, le toit ?
+enfant-m|Oui, papa.
+maman|On entre, Raphaël ?
 enfant-m|On entre.
+copain|On entre.
 narrateur|Ils se glissent dessous.
 narrateur|La lumière devient jaune.
-narrateur|Le drap sent encore le soleil.
-narrateur|On entend l'horloge, plus loin.
 enfant-m|On est dedans.
 copain|C'est chaud.
-papa|Deux biscuits, pour les capitaines.
+papa|Deux biscuits, pour vous.
 narrateur|Papa passe les biscuits sous le bord.
-narrateur|Ça croque tout doux.
+narrateur|Ça croque, un peu.
 narrateur|Une miette tombe sur le tapis.
-papa|Bravo, Raphaël.
-papa|Tu as fermé le trou.
-papa|Vous jouez.
-papa|L'amitié ne dépend pas de la forme.
-narrateur|Une chaise glisse un peu.
-enfant-m|Attends.
-narrateur|Aniss la recale.
-narrateur|La cabane tient.
-enfant-m|Elle est solide.</t>
+maman|La miette est sur le tapis ?
+enfant-m|Oui, maman.
+narrateur|Le ventre de Raphaël se desserre.
+narrateur|Les épaules se relèvent un peu.
+papa|On reste sous le drap ?
+enfant-m|Oui.
+maman|Tes mains sont au chaud ?
+enfant-m|Un peu, maman.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>drap,biscuit</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1837,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On reste encore un peu ? Oui. Un peu. L'horloge tic plus loin. La mouche a quitté la vitre. Tu as fini tes biscuits ? Oui, papa. Ils sortent à reculons. Le salon redevient grand. Le rai de poussière est encore là. Raphaël plie le drap. Aniss plie le torchon. Merci, Aniss. Merci, Raphaël. Le drap sent encore le soleil. La pince à linge reste sur la chaise.</t>
+          <t>Raphaël veut un toit plus grand. Une grande cabane, maintenant ! Il tire une chaise trop vite. Il regarde les épaules d'Aniss, trop longtemps. Un rire revient dans sa bouche. Attends. Aniss lâche le bois. La chaise glisse sur le tapis. Ça tombe ! Le drap tombe sur Aniss. Raphaël avance les mains, trop vite. Puis il s'arrête net. Raphaël refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe la chaise, un instant. Il écoute le tic de l'horloge. Sur le bois, un éclat de chaise luit. Là, sur le bois. Tu tiens, Aniss ? Aniss ne dit rien. Il reprend le dossier, sans parler. Oui. Ils recalent la chaise, sans se presser. Le drap redevient un toit. Le toit est jaune ? Il est jaune. Il est beau. La pince tient le coin. Elle tient. Tu restes un peu ? Oui, papa. L'horloge tic plus loin. On l'entend ? Oui, sous le drap. La cabane sent le soleil. Elle colle aux doigts. Comme le fil, oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On reste encore un peu ? Oui. Un peu. L'horloge tic plus loin. La mouche a quitté la vitre. Tu as fini tes biscuits ? Oui, papa. Ils sortent à reculons. Le salon redevient grand. Le rai de poussière est encore là. Raphaël plie le drap. Aniss plie le torchon. Merci, Aniss. Merci, Raphaël. Le drap sent encore le soleil. La pince à linge reste sur la chaise.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël veut un toit plus grand. Une grande cabane, maintenant ! Il tire une chaise trop vite. Il regarde les épaules d'Aniss, trop longtemps. Un rire revient dans sa bouche. Attends. Aniss lâche le bois. La chaise glisse sur le tapis. Ça tombe ! Le drap tombe sur Aniss. Raphaël avance les mains, trop vite. Puis il s'arrête net. Raphaël refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe la chaise, un instant. Il écoute le tic de l'horloge. Sur le bois, un &lt;emphasis level="moderate"&gt;éclat de chaise&lt;/emphasis&gt; luit. Là, sur le bois. Tu tiens, Aniss ? Aniss ne dit rien. Il reprend le dossier, sans parler. Oui. Ils recalent la chaise, sans se presser. Le drap redevient un toit. Le toit est jaune ? Il est jaune. Il est beau. La pince tient le coin. Elle tient. Tu restes un peu ? Oui, papa. L'horloge tic plus loin. On l'entend ? Oui, sous le drap. La cabane sent le soleil. Elle colle aux doigts. Comme le fil, oui.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Prune essuie ses &lt;emphasis&gt;main&lt;/emphasis&gt;s. [pause]</t>
+          <t>Raphaël veut un toit plus grand. Une grande cabane, maintenant ! Il tire une chaise trop vite. Il regarde les épaules d'Aniss, trop longtemps. Un rire revient dans sa bouche. Attends. Aniss lâche le bois. La chaise glisse sur le tapis. Ça tombe ! Le drap tombe sur Aniss. Raphaël avance les mains, trop vite. Puis il s'arrête net. Raphaël refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe la chaise, un instant. Il écoute le tic de l'horloge. Sur le bois, un &lt;emphasis&gt;éclat de chaise&lt;/emphasis&gt; luit. Là, sur le bois. Tu tiens, Aniss ? Aniss ne dit rien. Il reprend le dossier, sans parler. Oui. Ils recalent la chaise, sans se presser. Le drap redevient un toit. Le toit est jaune ? Il est jaune. Il est beau. La pince tient le coin. Elle tient. Tu restes un peu ? Oui, papa. L'horloge tic plus loin. On l'entend ? Oui, sous le drap. La cabane sent le soleil. Elle colle aux doigts. Comme le fil, oui. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1823,7 +1894,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1831,10 +1902,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1857,30 +1928,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>éclat de chaise</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1889,10 +1960,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1903,25 +1974,56 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_retrouve_l_eclat; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>papa|On reste encore un peu ?
-enfant-m|Oui.
-copain|Un peu.
-narrateur|L'horloge tic plus loin.
-narrateur|La mouche a quitté la vitre.
-papa|Tu as fini tes biscuits ?
+          <t>narrateur|Raphaël veut un toit plus grand.
+enfant-m|Une grande cabane, maintenant !
+narrateur|Il tire une chaise trop vite.
+narrateur|Il regarde les épaules d'Aniss, trop longtemps.
+narrateur|Un rire revient dans sa bouche.
+copain|Attends.
+narrateur|Aniss lâche le bois.
+narrateur|La chaise glisse sur le tapis.
+enfant-m|Ça tombe !
+narrateur|Le drap tombe sur Aniss.
+narrateur|Raphaël avance les mains, trop vite.
+narrateur|Puis il s'arrête net.
+narrateur|Raphaël refuse de foncer, cette fois.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Personne ne dit la suite.
+narrateur|Il observe la chaise, un instant.
+narrateur|Il écoute le tic de l'horloge.
+narrateur|Sur le bois, un éclat de chaise luit.
+enfant-m|Là, sur le bois.
+enfant-m|Tu tiens, Aniss ?
+narrateur|Aniss ne dit rien.
+narrateur|Il reprend le dossier, sans parler.
+copain|Oui.
+narrateur|Ils recalent la chaise, sans se presser.
+narrateur|Le drap redevient un toit.
+maman|Le toit est jaune ?
+enfant-m|Il est jaune.
+copain|Il est beau.
+narrateur|La pince tient le coin.
+enfant-m|Elle tient.
+papa|Tu restes un peu ?
 enfant-m|Oui, papa.
-narrateur|Ils sortent à reculons.
-narrateur|Le salon redevient grand.
-narrateur|Le rai de poussière est encore là.
-narrateur|Raphaël plie le drap.
-narrateur|Aniss plie le torchon.
-enfant-m|Merci, Aniss.
-copain|Merci, Raphaël.
-papa|Le drap sent encore le soleil.
-narrateur|La pince à linge reste sur la chaise.</t>
+maman|L'horloge tic plus loin.
+enfant-m|On l'entend ?
+papa|Oui, sous le drap.
+narrateur|La cabane sent le soleil.
+enfant-m|Elle colle aux doigts.
+maman|Comme le fil, oui.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>chaise</t>
         </is>
       </c>
     </row>
@@ -1948,17 +2050,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a fait la cabane. On a mangé dedans. Vous avez joué. Le drap garde un peu de jaune.</t>
+          <t>Ils restent sous le drap. Maman recale un coin, sans bruit. On a fait une cabane, papa. Tu la vois, toi ? Oui, au milieu. On est bien, ici. Raphaël glisse le doigt sur le bois. On le sent, maman. Tu le sens sur tes doigts ? Oui, il est lisse. Le toit est jaune, Raphaël. Oui, avec Aniss. Le toit est resté. Le drap sent le soleil, un peu chaud. Il est là, maman. Oui, sur les chaises. La mouche a quitté la vitre. Un éclat de chaise tient sur le bois.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a fait la cabane. On a mangé dedans. Vous avez joué. Le drap garde un peu de jaune.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent sous le drap. Maman recale un coin, sans bruit. On a fait une cabane, papa. Tu la vois, toi ? Oui, au milieu. On est bien, ici. Raphaël glisse le doigt sur le bois. On le sent, maman. Tu le sens sur tes doigts ? Oui, il est lisse. Le toit est jaune, Raphaël. Oui, avec Aniss. Le toit est resté. Le drap sent le soleil, un peu chaud. Il est là, maman. Oui, sur les chaises. La mouche a quitté la vitre. Un &lt;emphasis level="moderate"&gt;éclat de chaise&lt;/emphasis&gt; tient sur le bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent sous le drap. Maman recale un coin, sans bruit. On a fait une cabane, papa. Tu la vois, toi ? Oui, au milieu. On est bien, ici. Raphaël glisse le doigt sur le bois. On le sent, maman. Tu le sens sur tes doigts ? Oui, il est lisse. Le toit est jaune, Raphaël. Oui, avec Aniss. Le toit est resté. Le drap sent le soleil, un peu chaud. Il est là, maman. Oui, sur les chaises. La mouche a quitté la vitre. Un &lt;emphasis&gt;éclat de chaise&lt;/emphasis&gt; tient sur le bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2005,7 +2107,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2013,10 +2115,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2025,12 +2127,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2039,17 +2141,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de chaise</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2058,11 +2164,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2071,27 +2177,50 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_le_bois; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a fait la cabane.
-copain|On a mangé dedans.
-papa|Vous avez joué.
-narrateur|Le drap garde un peu de jaune.</t>
+          <t>narrateur|Ils restent sous le drap.
+narrateur|Maman recale un coin, sans bruit.
+enfant-m|On a fait une cabane, papa.
+papa|Tu la vois, toi ?
+enfant-m|Oui, au milieu.
+maman|On est bien, ici.
+narrateur|Raphaël glisse le doigt sur le bois.
+enfant-m|On le sent, maman.
+maman|Tu le sens sur tes doigts ?
+enfant-m|Oui, il est lisse.
+papa|Le toit est jaune, Raphaël.
+enfant-m|Oui, avec Aniss.
+copain|Le toit est resté.
+narrateur|Le drap sent le soleil, un peu chaud.
+enfant-m|Il est là, maman.
+maman|Oui, sur les chaises.
+narrateur|La mouche a quitté la vitre.
+narrateur|Un éclat de chaise tient sur le bois.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>drap</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2197,6 +2326,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
